--- a/Day4_WhatIf_Analysis.xlsx
+++ b/Day4_WhatIf_Analysis.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://d.docs.live.net/fb1792ed99f55154/Documents/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="14_{7B87EF49-80BB-4F1E-BEEC-8BC333CC1938}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="1" documentId="14_{7B87EF49-80BB-4F1E-BEEC-8BC333CC1938}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{C2A9C474-E19A-4B23-B3E7-096CF36EE098}"/>
   <bookViews>
-    <workbookView xWindow="-120" yWindow="-120" windowWidth="20730" windowHeight="11160" activeTab="1" xr2:uid="{9BA0AC82-335E-48C8-BB48-23446EE89F7A}"/>
+    <workbookView xWindow="-120" yWindow="-120" windowWidth="20730" windowHeight="11160" activeTab="2" xr2:uid="{9BA0AC82-335E-48C8-BB48-23446EE89F7A}"/>
   </bookViews>
   <sheets>
     <sheet name="Scenario Summary" sheetId="2" r:id="rId1"/>
@@ -39,13 +39,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="42" uniqueCount="39">
-  <si>
-    <t>A1</t>
-  </si>
-  <si>
-    <t>A3</t>
-  </si>
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="48" uniqueCount="45">
   <si>
     <t>B3</t>
   </si>
@@ -156,13 +150,37 @@
   </si>
   <si>
     <t>Upper Confidence Bound(revenue)</t>
+  </si>
+  <si>
+    <t>Revenue planning what-if-analysis</t>
+  </si>
+  <si>
+    <t>Objective: Analyse how price and customer footfall affect revenue.</t>
+  </si>
+  <si>
+    <t>project findings</t>
+  </si>
+  <si>
+    <t>target revenue</t>
+  </si>
+  <si>
+    <t>price needed</t>
+  </si>
+  <si>
+    <t>expected customers</t>
+  </si>
+  <si>
+    <t>CONCLUSION</t>
+  </si>
+  <si>
+    <t>Revenue increases when price or customer footfall increases. Goal Seek helps find the price needed to reach a target, while Scenario Manager compares different sales situations.</t>
   </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
-  <fonts count="6" x14ac:knownFonts="1">
+  <fonts count="7" x14ac:knownFonts="1">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -208,6 +226,14 @@
       <family val="2"/>
       <scheme val="minor"/>
     </font>
+    <font>
+      <b/>
+      <sz val="11"/>
+      <color theme="1"/>
+      <name val="Calibri"/>
+      <family val="2"/>
+      <scheme val="minor"/>
+    </font>
   </fonts>
   <fills count="5">
     <fill>
@@ -235,7 +261,7 @@
       </patternFill>
     </fill>
   </fills>
-  <borders count="5">
+  <borders count="6">
     <border>
       <left/>
       <right/>
@@ -281,15 +307,27 @@
       </bottom>
       <diagonal/>
     </border>
+    <border>
+      <left style="thin">
+        <color indexed="64"/>
+      </left>
+      <right style="thin">
+        <color indexed="64"/>
+      </right>
+      <top style="thin">
+        <color indexed="64"/>
+      </top>
+      <bottom style="thin">
+        <color indexed="64"/>
+      </bottom>
+      <diagonal/>
+    </border>
   </borders>
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="16">
+  <cellXfs count="24">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyAlignment="1">
-      <alignment horizontal="left"/>
-    </xf>
     <xf numFmtId="2" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="2" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1"/>
@@ -320,6 +358,21 @@
       <alignment vertical="top" wrapText="1"/>
     </xf>
     <xf numFmtId="14" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="0" xfId="0" applyFont="1"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="1"/>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="5" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="5" xfId="0" applyBorder="1"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="5" xfId="0" applyNumberFormat="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left"/>
+    </xf>
+    <xf numFmtId="14" fontId="0" fillId="0" borderId="5" xfId="0" applyNumberFormat="1" applyBorder="1"/>
+    <xf numFmtId="14" fontId="0" fillId="0" borderId="5" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="5" xfId="0" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
+      <alignment horizontal="left" vertical="top" wrapText="1"/>
+    </xf>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
@@ -1822,204 +1875,204 @@
   <sheetData>
     <row r="1" spans="2:7" ht="15.75" thickBot="1" x14ac:dyDescent="0.3"/>
     <row r="2" spans="2:7" ht="15.75" x14ac:dyDescent="0.25">
-      <c r="B2" s="6" t="s">
+      <c r="B2" s="5" t="s">
+        <v>26</v>
+      </c>
+      <c r="C2" s="5"/>
+      <c r="D2" s="10"/>
+      <c r="E2" s="10"/>
+      <c r="F2" s="10"/>
+      <c r="G2" s="10"/>
+    </row>
+    <row r="3" spans="2:7" ht="15.75" collapsed="1" x14ac:dyDescent="0.25">
+      <c r="B3" s="4"/>
+      <c r="C3" s="4"/>
+      <c r="D3" s="11" t="s">
         <v>28</v>
       </c>
-      <c r="C2" s="6"/>
-      <c r="D2" s="11"/>
-      <c r="E2" s="11"/>
-      <c r="F2" s="11"/>
-      <c r="G2" s="11"/>
-    </row>
-    <row r="3" spans="2:7" ht="15.75" collapsed="1" x14ac:dyDescent="0.25">
-      <c r="B3" s="5"/>
-      <c r="C3" s="5"/>
-      <c r="D3" s="12" t="s">
+      <c r="E3" s="11" t="s">
+        <v>21</v>
+      </c>
+      <c r="F3" s="11" t="s">
+        <v>23</v>
+      </c>
+      <c r="G3" s="11" t="s">
+        <v>25</v>
+      </c>
+    </row>
+    <row r="4" spans="2:7" ht="33.75" hidden="1" outlineLevel="1" x14ac:dyDescent="0.25">
+      <c r="B4" s="7"/>
+      <c r="C4" s="7"/>
+      <c r="D4" s="2"/>
+      <c r="E4" s="13" t="s">
+        <v>22</v>
+      </c>
+      <c r="F4" s="13" t="s">
+        <v>24</v>
+      </c>
+      <c r="G4" s="13" t="s">
+        <v>24</v>
+      </c>
+    </row>
+    <row r="5" spans="2:7" x14ac:dyDescent="0.25">
+      <c r="B5" s="8" t="s">
+        <v>27</v>
+      </c>
+      <c r="C5" s="8"/>
+      <c r="D5" s="6"/>
+      <c r="E5" s="6"/>
+      <c r="F5" s="6"/>
+      <c r="G5" s="6"/>
+    </row>
+    <row r="6" spans="2:7" outlineLevel="1" x14ac:dyDescent="0.25">
+      <c r="B6" s="7"/>
+      <c r="C6" s="7" t="s">
+        <v>14</v>
+      </c>
+      <c r="D6" s="2">
+        <v>200</v>
+      </c>
+      <c r="E6" s="12">
+        <v>80</v>
+      </c>
+      <c r="F6" s="12">
+        <v>100</v>
+      </c>
+      <c r="G6" s="12">
+        <v>150</v>
+      </c>
+    </row>
+    <row r="7" spans="2:7" outlineLevel="1" x14ac:dyDescent="0.25">
+      <c r="B7" s="7"/>
+      <c r="C7" s="7" t="s">
+        <v>15</v>
+      </c>
+      <c r="D7" s="2">
+        <v>50</v>
+      </c>
+      <c r="E7" s="12">
         <v>30</v>
       </c>
-      <c r="E3" s="12" t="s">
-        <v>23</v>
-      </c>
-      <c r="F3" s="12" t="s">
-        <v>25</v>
-      </c>
-      <c r="G3" s="12" t="s">
-        <v>27</v>
-      </c>
-    </row>
-    <row r="4" spans="2:7" ht="33.75" hidden="1" outlineLevel="1" x14ac:dyDescent="0.25">
-      <c r="B4" s="8"/>
-      <c r="C4" s="8"/>
-      <c r="D4" s="3"/>
-      <c r="E4" s="14" t="s">
-        <v>24</v>
-      </c>
-      <c r="F4" s="14" t="s">
-        <v>26</v>
-      </c>
-      <c r="G4" s="14" t="s">
-        <v>26</v>
-      </c>
-    </row>
-    <row r="5" spans="2:7" x14ac:dyDescent="0.25">
-      <c r="B5" s="9" t="s">
+      <c r="F7" s="12">
+        <v>50</v>
+      </c>
+      <c r="G7" s="12">
+        <v>80</v>
+      </c>
+    </row>
+    <row r="8" spans="2:7" x14ac:dyDescent="0.25">
+      <c r="B8" s="8" t="s">
         <v>29</v>
       </c>
-      <c r="C5" s="9"/>
-      <c r="D5" s="7"/>
-      <c r="E5" s="7"/>
-      <c r="F5" s="7"/>
-      <c r="G5" s="7"/>
-    </row>
-    <row r="6" spans="2:7" outlineLevel="1" x14ac:dyDescent="0.25">
-      <c r="B6" s="8"/>
-      <c r="C6" s="8" t="s">
+      <c r="C8" s="8"/>
+      <c r="D8" s="6"/>
+      <c r="E8" s="6"/>
+      <c r="F8" s="6"/>
+      <c r="G8" s="6"/>
+    </row>
+    <row r="9" spans="2:7" outlineLevel="1" x14ac:dyDescent="0.25">
+      <c r="B9" s="7"/>
+      <c r="C9" s="7" t="s">
         <v>16</v>
       </c>
-      <c r="D6" s="3">
-        <v>200</v>
-      </c>
-      <c r="E6" s="13">
-        <v>80</v>
-      </c>
-      <c r="F6" s="13">
-        <v>100</v>
-      </c>
-      <c r="G6" s="13">
-        <v>150</v>
-      </c>
-    </row>
-    <row r="7" spans="2:7" outlineLevel="1" x14ac:dyDescent="0.25">
-      <c r="B7" s="8"/>
-      <c r="C7" s="8" t="s">
+      <c r="D9" s="2">
+        <v>4000</v>
+      </c>
+      <c r="E9" s="2">
+        <v>2400</v>
+      </c>
+      <c r="F9" s="2">
+        <v>4000</v>
+      </c>
+      <c r="G9" s="2">
+        <v>6400</v>
+      </c>
+    </row>
+    <row r="10" spans="2:7" outlineLevel="1" x14ac:dyDescent="0.25">
+      <c r="B10" s="7"/>
+      <c r="C10" s="7" t="s">
         <v>17</v>
       </c>
-      <c r="D7" s="3">
-        <v>50</v>
-      </c>
-      <c r="E7" s="13">
-        <v>30</v>
-      </c>
-      <c r="F7" s="13">
-        <v>50</v>
-      </c>
-      <c r="G7" s="13">
-        <v>80</v>
-      </c>
-    </row>
-    <row r="8" spans="2:7" x14ac:dyDescent="0.25">
-      <c r="B8" s="9" t="s">
-        <v>31</v>
-      </c>
-      <c r="C8" s="9"/>
-      <c r="D8" s="7"/>
-      <c r="E8" s="7"/>
-      <c r="F8" s="7"/>
-      <c r="G8" s="7"/>
-    </row>
-    <row r="9" spans="2:7" outlineLevel="1" x14ac:dyDescent="0.25">
-      <c r="B9" s="8"/>
-      <c r="C9" s="8" t="s">
+      <c r="D10" s="2">
+        <v>5000</v>
+      </c>
+      <c r="E10" s="2">
+        <v>3000</v>
+      </c>
+      <c r="F10" s="2">
+        <v>5000</v>
+      </c>
+      <c r="G10" s="2">
+        <v>8000</v>
+      </c>
+    </row>
+    <row r="11" spans="2:7" outlineLevel="1" x14ac:dyDescent="0.25">
+      <c r="B11" s="7"/>
+      <c r="C11" s="7" t="s">
         <v>18</v>
       </c>
-      <c r="D9" s="3">
-        <v>4000</v>
-      </c>
-      <c r="E9" s="3">
-        <v>2400</v>
-      </c>
-      <c r="F9" s="3">
-        <v>4000</v>
-      </c>
-      <c r="G9" s="3">
-        <v>6400</v>
-      </c>
-    </row>
-    <row r="10" spans="2:7" outlineLevel="1" x14ac:dyDescent="0.25">
-      <c r="B10" s="8"/>
-      <c r="C10" s="8" t="s">
+      <c r="D11" s="2">
+        <v>7500</v>
+      </c>
+      <c r="E11" s="2">
+        <v>4500</v>
+      </c>
+      <c r="F11" s="2">
+        <v>7500</v>
+      </c>
+      <c r="G11" s="2">
+        <v>12000</v>
+      </c>
+    </row>
+    <row r="12" spans="2:7" outlineLevel="1" x14ac:dyDescent="0.25">
+      <c r="B12" s="7"/>
+      <c r="C12" s="7" t="s">
         <v>19</v>
       </c>
-      <c r="D10" s="3">
-        <v>5000</v>
-      </c>
-      <c r="E10" s="3">
-        <v>3000</v>
-      </c>
-      <c r="F10" s="3">
-        <v>5000</v>
-      </c>
-      <c r="G10" s="3">
-        <v>8000</v>
-      </c>
-    </row>
-    <row r="11" spans="2:7" outlineLevel="1" x14ac:dyDescent="0.25">
-      <c r="B11" s="8"/>
-      <c r="C11" s="8" t="s">
+      <c r="D12" s="2">
+        <v>10000</v>
+      </c>
+      <c r="E12" s="2">
+        <v>6000</v>
+      </c>
+      <c r="F12" s="2">
+        <v>10000</v>
+      </c>
+      <c r="G12" s="2">
+        <v>16000</v>
+      </c>
+    </row>
+    <row r="13" spans="2:7" ht="15.75" outlineLevel="1" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="B13" s="9"/>
+      <c r="C13" s="9" t="s">
         <v>20</v>
       </c>
-      <c r="D11" s="3">
+      <c r="D13" s="3">
+        <v>12500</v>
+      </c>
+      <c r="E13" s="3">
         <v>7500</v>
       </c>
-      <c r="E11" s="3">
-        <v>4500</v>
-      </c>
-      <c r="F11" s="3">
-        <v>7500</v>
-      </c>
-      <c r="G11" s="3">
-        <v>12000</v>
-      </c>
-    </row>
-    <row r="12" spans="2:7" outlineLevel="1" x14ac:dyDescent="0.25">
-      <c r="B12" s="8"/>
-      <c r="C12" s="8" t="s">
-        <v>21</v>
-      </c>
-      <c r="D12" s="3">
-        <v>10000</v>
-      </c>
-      <c r="E12" s="3">
-        <v>6000</v>
-      </c>
-      <c r="F12" s="3">
-        <v>10000</v>
-      </c>
-      <c r="G12" s="3">
-        <v>16000</v>
-      </c>
-    </row>
-    <row r="13" spans="2:7" ht="15.75" outlineLevel="1" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="B13" s="10"/>
-      <c r="C13" s="10" t="s">
-        <v>22</v>
-      </c>
-      <c r="D13" s="4">
+      <c r="F13" s="3">
         <v>12500</v>
       </c>
-      <c r="E13" s="4">
-        <v>7500</v>
-      </c>
-      <c r="F13" s="4">
-        <v>12500</v>
-      </c>
-      <c r="G13" s="4">
+      <c r="G13" s="3">
         <v>20000</v>
       </c>
     </row>
     <row r="14" spans="2:7" x14ac:dyDescent="0.25">
       <c r="B14" t="s">
-        <v>32</v>
+        <v>30</v>
       </c>
     </row>
     <row r="15" spans="2:7" x14ac:dyDescent="0.25">
       <c r="B15" t="s">
-        <v>33</v>
+        <v>31</v>
       </c>
     </row>
     <row r="16" spans="2:7" x14ac:dyDescent="0.25">
       <c r="B16" t="s">
-        <v>34</v>
+        <v>32</v>
       </c>
     </row>
   </sheetData>
@@ -2042,23 +2095,23 @@
   <sheetData>
     <row r="1" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A1" t="s">
+        <v>33</v>
+      </c>
+      <c r="B1" t="s">
+        <v>13</v>
+      </c>
+      <c r="C1" t="s">
+        <v>34</v>
+      </c>
+      <c r="D1" t="s">
         <v>35</v>
       </c>
-      <c r="B1" t="s">
-        <v>15</v>
-      </c>
-      <c r="C1" t="s">
+      <c r="E1" t="s">
         <v>36</v>
       </c>
-      <c r="D1" t="s">
-        <v>37</v>
-      </c>
-      <c r="E1" t="s">
-        <v>38</v>
-      </c>
     </row>
     <row r="2" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A2" s="15">
+      <c r="A2" s="14">
         <v>46023</v>
       </c>
       <c r="B2">
@@ -2066,7 +2119,7 @@
       </c>
     </row>
     <row r="3" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A3" s="15">
+      <c r="A3" s="14">
         <v>46024</v>
       </c>
       <c r="B3">
@@ -2074,7 +2127,7 @@
       </c>
     </row>
     <row r="4" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A4" s="15">
+      <c r="A4" s="14">
         <v>46025</v>
       </c>
       <c r="B4">
@@ -2082,7 +2135,7 @@
       </c>
     </row>
     <row r="5" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A5" s="15">
+      <c r="A5" s="14">
         <v>46026</v>
       </c>
       <c r="B5">
@@ -2090,7 +2143,7 @@
       </c>
     </row>
     <row r="6" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A6" s="15">
+      <c r="A6" s="14">
         <v>46027</v>
       </c>
       <c r="B6">
@@ -2098,7 +2151,7 @@
       </c>
     </row>
     <row r="7" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A7" s="15">
+      <c r="A7" s="14">
         <v>46028</v>
       </c>
       <c r="B7">
@@ -2107,43 +2160,43 @@
       <c r="C7">
         <v>8000</v>
       </c>
-      <c r="D7" s="2">
+      <c r="D7" s="1">
         <v>8000</v>
       </c>
-      <c r="E7" s="2">
+      <c r="E7" s="1">
         <v>8000</v>
       </c>
     </row>
     <row r="8" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A8" s="15">
+      <c r="A8" s="14">
         <v>46029</v>
       </c>
       <c r="C8">
         <f>_xlfn.FORECAST.ETS(A8,$B$2:$B$7,$A$2:$A$7,1,1)</f>
         <v>8599.9961412839966</v>
       </c>
-      <c r="D8" s="2">
+      <c r="D8" s="1">
         <f>C8-_xlfn.FORECAST.ETS.CONFINT(A8,$B$2:$B$7,$A$2:$A$7,0.95,1,1)</f>
         <v>7929.6216813824358</v>
       </c>
-      <c r="E8" s="2">
+      <c r="E8" s="1">
         <f>C8+_xlfn.FORECAST.ETS.CONFINT(A8,$B$2:$B$7,$A$2:$A$7,0.95,1,1)</f>
         <v>9270.3706011855575</v>
       </c>
     </row>
     <row r="9" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A9" s="15">
+      <c r="A9" s="14">
         <v>46030</v>
       </c>
       <c r="C9">
         <f>_xlfn.FORECAST.ETS(A9,$B$2:$B$7,$A$2:$A$7,1,1)</f>
         <v>9199.9956515489303</v>
       </c>
-      <c r="D9" s="2">
+      <c r="D9" s="1">
         <f>C9-_xlfn.FORECAST.ETS.CONFINT(A9,$B$2:$B$7,$A$2:$A$7,0.95,1,1)</f>
         <v>8529.6181749690877</v>
       </c>
-      <c r="E9" s="2">
+      <c r="E9" s="1">
         <f>C9+_xlfn.FORECAST.ETS.CONFINT(A9,$B$2:$B$7,$A$2:$A$7,0.95,1,1)</f>
         <v>9870.3731281287728</v>
       </c>
@@ -2159,182 +2212,238 @@
 
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{7E4061B8-7DDD-409A-BA3B-B08BC062DE89}">
-  <dimension ref="A1:E17"/>
+  <dimension ref="A1:E26"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
-    <col min="1" max="1" width="18" customWidth="1"/>
+    <col min="1" max="1" width="22.42578125" customWidth="1"/>
     <col min="2" max="2" width="26.85546875" customWidth="1"/>
     <col min="3" max="3" width="23.7109375" customWidth="1"/>
     <col min="4" max="4" width="18.7109375" customWidth="1"/>
     <col min="5" max="5" width="18.28515625" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A1" t="s">
+    <row r="1" spans="1:5" ht="30" x14ac:dyDescent="0.25">
+      <c r="A1" s="17" t="s">
+        <v>37</v>
+      </c>
+      <c r="B1" s="18" t="s">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="2" spans="1:5" ht="45" x14ac:dyDescent="0.25">
+      <c r="A2" s="17" t="s">
+        <v>38</v>
+      </c>
+      <c r="B2" s="18" t="s">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="3" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A3" s="18" t="s">
         <v>0</v>
       </c>
-      <c r="B1" t="s">
-        <v>7</v>
-      </c>
-    </row>
-    <row r="2" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A2" t="s">
-        <v>1</v>
-      </c>
-      <c r="B2" t="s">
-        <v>8</v>
-      </c>
-    </row>
-    <row r="3" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A3" t="s">
-        <v>2</v>
-      </c>
-      <c r="B3" s="1">
+      <c r="B3" s="19">
         <v>200</v>
       </c>
-      <c r="D3" t="s">
-        <v>14</v>
-      </c>
-      <c r="E3">
+      <c r="D3" s="18" t="s">
+        <v>12</v>
+      </c>
+      <c r="E3" s="18">
         <f>B7</f>
         <v>10000</v>
       </c>
     </row>
     <row r="4" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A4" t="s">
-        <v>3</v>
-      </c>
-      <c r="B4" t="s">
-        <v>9</v>
-      </c>
-      <c r="D4">
+      <c r="A4" s="18" t="s">
+        <v>1</v>
+      </c>
+      <c r="B4" s="18" t="s">
+        <v>7</v>
+      </c>
+      <c r="D4" s="18">
         <v>80</v>
       </c>
-      <c r="E4">
+      <c r="E4" s="18">
         <f t="dataTable" ref="E4:E8" dt2D="0" dtr="0" r1="B3"/>
         <v>4000</v>
       </c>
     </row>
     <row r="5" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A5" t="s">
+      <c r="A5" s="18" t="s">
+        <v>2</v>
+      </c>
+      <c r="B5" s="19">
+        <v>50</v>
+      </c>
+      <c r="D5" s="18">
+        <v>100</v>
+      </c>
+      <c r="E5" s="18">
+        <v>5000</v>
+      </c>
+    </row>
+    <row r="6" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A6" s="18" t="s">
+        <v>3</v>
+      </c>
+      <c r="B6" s="18" t="s">
+        <v>8</v>
+      </c>
+      <c r="D6" s="18">
+        <v>150</v>
+      </c>
+      <c r="E6" s="18">
+        <v>7500</v>
+      </c>
+    </row>
+    <row r="7" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A7" s="18" t="s">
         <v>4</v>
       </c>
-      <c r="B5" s="1">
-        <v>50</v>
-      </c>
-      <c r="D5">
-        <v>100</v>
-      </c>
-      <c r="E5">
-        <v>5000</v>
-      </c>
-    </row>
-    <row r="6" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A6" t="s">
-        <v>5</v>
-      </c>
-      <c r="B6" t="s">
-        <v>10</v>
-      </c>
-      <c r="D6">
-        <v>150</v>
-      </c>
-      <c r="E6">
-        <v>7500</v>
-      </c>
-    </row>
-    <row r="7" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A7" t="s">
-        <v>6</v>
-      </c>
-      <c r="B7" s="1">
+      <c r="B7" s="19">
         <f>B3*B5</f>
         <v>10000</v>
       </c>
-      <c r="D7">
+      <c r="D7" s="18">
         <v>200</v>
       </c>
-      <c r="E7">
+      <c r="E7" s="18">
         <v>10000</v>
       </c>
     </row>
     <row r="8" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A8" t="s">
+      <c r="A8" s="18" t="s">
+        <v>9</v>
+      </c>
+      <c r="B8" s="18" t="s">
         <v>11</v>
       </c>
-      <c r="B8" t="s">
+      <c r="D8" s="18">
+        <v>250</v>
+      </c>
+      <c r="E8" s="18">
+        <v>12500</v>
+      </c>
+    </row>
+    <row r="9" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A9" s="18" t="s">
+        <v>10</v>
+      </c>
+      <c r="B9" s="18">
+        <v>10000</v>
+      </c>
+    </row>
+    <row r="11" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A11" s="15" t="s">
+        <v>39</v>
+      </c>
+      <c r="D11" s="18" t="s">
+        <v>33</v>
+      </c>
+      <c r="E11" s="18" t="s">
         <v>13</v>
       </c>
-      <c r="D8">
-        <v>250</v>
-      </c>
-      <c r="E8">
-        <v>12500</v>
-      </c>
-    </row>
-    <row r="9" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A9" t="s">
-        <v>12</v>
-      </c>
-      <c r="B9">
+    </row>
+    <row r="12" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A12" s="15" t="s">
+        <v>40</v>
+      </c>
+      <c r="B12">
         <v>10000</v>
       </c>
-    </row>
-    <row r="11" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="D11" t="s">
-        <v>35</v>
-      </c>
-      <c r="E11" t="s">
-        <v>15</v>
-      </c>
-    </row>
-    <row r="12" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="D12" s="15">
+      <c r="D12" s="20">
         <v>46023</v>
       </c>
-      <c r="E12">
+      <c r="E12" s="18">
         <v>5000</v>
       </c>
     </row>
     <row r="13" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="D13" s="15">
+      <c r="A13" s="15" t="s">
+        <v>41</v>
+      </c>
+      <c r="B13">
+        <f>B3</f>
+        <v>200</v>
+      </c>
+      <c r="D13" s="20">
         <v>46024</v>
       </c>
-      <c r="E13">
+      <c r="E13" s="18">
         <v>6000</v>
       </c>
     </row>
-    <row r="14" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="D14" s="15">
+    <row r="14" spans="1:5" s="16" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="A14" s="15" t="s">
+        <v>42</v>
+      </c>
+      <c r="B14" s="16">
+        <f>B5</f>
+        <v>50</v>
+      </c>
+      <c r="D14" s="21">
         <v>46025</v>
       </c>
-      <c r="E14">
+      <c r="E14" s="22">
         <v>5500</v>
       </c>
     </row>
     <row r="15" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="D15" s="15">
+      <c r="D15" s="20">
         <v>46026</v>
       </c>
-      <c r="E15">
+      <c r="E15" s="18">
         <v>7000</v>
       </c>
     </row>
     <row r="16" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="D16" s="15">
+      <c r="A16" s="15" t="s">
+        <v>43</v>
+      </c>
+      <c r="D16" s="20">
         <v>46027</v>
       </c>
-      <c r="E16">
+      <c r="E16" s="18">
         <v>7500</v>
       </c>
     </row>
-    <row r="17" spans="4:5" x14ac:dyDescent="0.25">
-      <c r="D17" s="15">
+    <row r="17" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A17" s="23" t="s">
+        <v>44</v>
+      </c>
+      <c r="D17" s="20">
         <v>46028</v>
       </c>
-      <c r="E17">
+      <c r="E17" s="18">
         <v>8000</v>
       </c>
+    </row>
+    <row r="18" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A18" s="23"/>
+    </row>
+    <row r="19" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A19" s="23"/>
+    </row>
+    <row r="20" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A20" s="23"/>
+    </row>
+    <row r="21" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A21" s="23"/>
+    </row>
+    <row r="22" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A22" s="23"/>
+    </row>
+    <row r="23" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A23" s="23"/>
+    </row>
+    <row r="24" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A24" s="23"/>
+    </row>
+    <row r="25" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A25" s="23"/>
+    </row>
+    <row r="26" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A26" s="23"/>
     </row>
   </sheetData>
   <scenarios current="0" sqref="E4 E5 E6 E7 E8">
@@ -2351,6 +2460,10 @@
       <inputCells r="B5" val="80"/>
     </scenario>
   </scenarios>
+  <mergeCells count="1">
+    <mergeCell ref="A17:A26"/>
+  </mergeCells>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+  <pageSetup orientation="portrait" r:id="rId1"/>
 </worksheet>
 </file>